--- a/project3_part1/tb/crp_results/crp_tables_for_report.xlsx
+++ b/project3_part1/tb/crp_results/crp_tables_for_report.xlsx
@@ -8,9 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRP Tables" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Single_Chip_HD" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'CRP Tables'!$A$1:$B$303</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Single_Chip_HD'!$A$5:$I$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Single_Chip_HD'!$A$1:$I$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.0000&quot;%&quot;"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,8 +43,24 @@
       <name val="Consolas"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="0017365D"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0017365D"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="0017365D"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +75,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EDF1F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF1F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F3F6"/>
       </patternFill>
     </fill>
   </fills>
@@ -115,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -128,6 +165,36 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3931,4 +3998,628 @@
   <pageMargins left="0.3" right="0.3" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Single-chip Hamming distance</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="n"/>
+      <c r="C1" s="7" t="n"/>
+      <c r="D1" s="7" t="n"/>
+      <c r="E1" s="7" t="n"/>
+      <c r="F1" s="7" t="n"/>
+      <c r="G1" s="7" t="n"/>
+      <c r="H1" s="7" t="n"/>
+      <c r="I1" s="7" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Different-challenge variation compares responses within one PUF. Same-challenge repeatability compares the two recorded runs of each challenge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Different-challenge variation</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>Same-challenge repeatability</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="n"/>
+      <c r="I4" s="12" t="n"/>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Challenge pairs</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Mean HD (bits)</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Mean HD (%)</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Min HD (bits)</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>Max HD (bits)</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>Repeat comparisons</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>Repeat mean HD (bits)</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>Repeat mean HD (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>PUF_00</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>15.64166666666667</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>48.88020833333334</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>PUF_01</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>15.74166666666667</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>49.19270833333334</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>PUF_02</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>15.71666666666667</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>49.11458333333334</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>PUF_03</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>15.91666666666667</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>49.73958333333333</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>PUF_04</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>15.64166666666667</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>48.88020833333334</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H10" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>PUF_05</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>14.98333333333333</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>46.82291666666666</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="21" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>PUF_06</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>15.40833333333333</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>48.15104166666666</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>PUF_07</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>15.68333333333333</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>49.01041666666666</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="21" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>PUF_08</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>16.36666666666667</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>51.14583333333334</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="21" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>PUF_09</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>15.96666666666667</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>49.89583333333334</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H15" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>PUF_10</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C16" s="16" t="n">
+        <v>15.875</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>49.609375</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H16" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>PUF_11</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C17" s="16" t="n">
+        <v>16.23333333333333</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>50.72916666666667</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H17" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>PUF_12</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C18" s="16" t="n">
+        <v>16.175</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>50.546875</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H18" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>PUF_13</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>16.375</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>51.171875</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="G19" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="21" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>PUF_14</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C20" s="16" t="n">
+        <v>15.90833333333333</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>49.71354166666666</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="G20" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H20" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>PUF_15</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>16.09166666666667</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>50.28645833333333</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="G21" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Percentages are stored as percentage values: 50 displays as 50.0000%. Zero repeat HD means the recorded responses matched across both runs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:I21"/>
+  <mergeCells count="5">
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="G4:I4"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/project3_part1/tb/crp_results/crp_tables_for_report.xlsx
+++ b/project3_part1/tb/crp_results/crp_tables_for_report.xlsx
@@ -9,11 +9,17 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRP Tables" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Single_Chip_HD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Multi_Chip_HD" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Multi_Chip_Pairs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Multi_Chip_Matrix" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'CRP Tables'!$A$1:$B$303</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Single_Chip_HD'!$A$5:$I$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Single_Chip_HD'!$A$1:$I$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Multi_Chip_HD'!$A$1:$F$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Multi_Chip_Pairs'!$A$1:$I$124</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Multi_Chip_Matrix'!$A$1:$Q$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -152,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -195,6 +201,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4026,14 +4047,6 @@
           <t>Single-chip Hamming distance</t>
         </is>
       </c>
-      <c r="B1" s="7" t="n"/>
-      <c r="C1" s="7" t="n"/>
-      <c r="D1" s="7" t="n"/>
-      <c r="E1" s="7" t="n"/>
-      <c r="F1" s="7" t="n"/>
-      <c r="G1" s="7" t="n"/>
-      <c r="H1" s="7" t="n"/>
-      <c r="I1" s="7" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
@@ -4042,23 +4055,18 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="24" customHeight="1">
       <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Different-challenge variation</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
       <c r="G4" s="11" t="inlineStr">
         <is>
           <t>Same-challenge repeatability</t>
         </is>
       </c>
-      <c r="H4" s="12" t="n"/>
-      <c r="I4" s="12" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
@@ -4603,6 +4611,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
@@ -4622,4 +4631,5550 @@
   <pageMargins left="0.25" right="0.25" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Multi-chip Hamming distance</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="n"/>
+      <c r="C1" s="7" t="n"/>
+      <c r="D1" s="7" t="n"/>
+      <c r="E1" s="7" t="n"/>
+      <c r="F1" s="7" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Different PUF configurations are compared using the same challenge. 120 distinct PUF pairs × 16 matched challenges = 1,920 comparisons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Challenge</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Comparisons</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Mean HD (bits)</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Mean HD (%)</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Min HD (bits)</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Max HD (bits)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>[0x0] 0000</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>15.90833333333333</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>49.71354166666666</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" ht="21" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>[0x1] 0001</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>47.96875</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>[0x2] 0010</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>50.46874999999999</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>[0x3] 0011</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>15.95833333333333</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>49.86979166666667</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>[0x4] 0100</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>15.13333333333333</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>47.29166666666666</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>[0x5] 0101</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>15.69166666666667</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>49.03645833333334</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>[0x6] 0110</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>15.84166666666667</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>49.50520833333334</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" ht="21" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>[0x7] 0111</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>15.48333333333333</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>48.38541666666666</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>[0x8] 1000</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>16.38333333333333</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>51.19791666666666</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" ht="21" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>[0x9] 1001</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>15.68333333333333</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>49.01041666666666</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" ht="21" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>[0xA] 1010</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>16.16666666666667</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>50.52083333333334</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>[0xB] 1011</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C16" s="16" t="n">
+        <v>16.03333333333333</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>50.10416666666667</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>[0xC] 1100</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C17" s="16" t="n">
+        <v>15.725</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>49.140625</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>[0xD] 1101</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C18" s="16" t="n">
+        <v>15.38333333333333</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>48.07291666666666</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>[0xE] 1110</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>15.83333333333333</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>49.47916666666667</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" ht="21" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>[0xF] 1111</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="C20" s="16" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>49.6875</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>1920</v>
+      </c>
+      <c r="C21" s="20" t="n">
+        <v>15.7890625</v>
+      </c>
+      <c r="D21" s="21" t="n">
+        <v>49.3408203125</v>
+      </c>
+      <c r="E21" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I124"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Multi-chip device-pair comparison</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="n"/>
+      <c r="C1" s="7" t="n"/>
+      <c r="D1" s="7" t="n"/>
+      <c r="E1" s="7" t="n"/>
+      <c r="F1" s="7" t="n"/>
+      <c r="G1" s="7" t="n"/>
+      <c r="H1" s="7" t="n"/>
+      <c r="I1" s="7" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Each row averages 16 matched challenges. Combined HD sums those comparisons across 512 actual response bits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>PUF A</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>PUF B</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Matched challenges</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Mean HD (bits)</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Mean HD (%)</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Min HD (bits)</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Max HD (bits)</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Combined HD (bits)</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Combined response bits</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>PUF_00</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>PUF_01</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>15.375</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>48.046875</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>246</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="6" ht="21" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>PUF_00</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>PUF_02</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>16.0625</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>50.1953125</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>257</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>PUF_00</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>PUF_03</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>15.6875</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>49.0234375</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>251</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>PUF_00</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>PUF_04</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>46.09375</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>236</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>PUF_00</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>PUF_05</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>16.9375</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>52.9296875</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>271</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>PUF_00</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>PUF_06</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>15.625</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>48.828125</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>250</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>PUF_00</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>PUF_07</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>15.5625</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>48.6328125</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>249</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="12" ht="21" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>PUF_00</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>PUF_08</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>17.6875</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>55.2734375</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>283</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>PUF_00</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>PUF_09</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>14.3125</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>44.7265625</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>229</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="14" ht="21" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>PUF_00</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>PUF_10</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>48.4375</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>248</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="15" ht="21" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>PUF_00</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>PUF_11</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>15.9375</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>49.8046875</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>255</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>PUF_00</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>PUF_12</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>16.125</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>50.390625</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>258</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>PUF_00</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>PUF_13</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>49.21875</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>252</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>PUF_00</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>PUF_14</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D18" s="16" t="n">
+        <v>13.625</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>42.578125</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>218</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>PUF_00</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>PUF_15</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>49.21875</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G19" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>252</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="20" ht="21" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>PUF_01</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>PUF_02</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <v>14.8125</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>46.2890625</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>237</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>PUF_01</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>PUF_03</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>15.9375</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>49.8046875</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G21" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>255</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="22" ht="21" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>PUF_01</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>PUF_04</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D22" s="16" t="n">
+        <v>15.875</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>49.609375</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>254</v>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>PUF_01</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>PUF_05</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D23" s="16" t="n">
+        <v>15.0625</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>47.0703125</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G23" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>241</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="24" ht="21" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>PUF_01</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>PUF_06</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>51.5625</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G24" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>264</v>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="25" ht="21" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>PUF_01</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>PUF_07</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>15.4375</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>48.2421875</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G25" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>247</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="26" ht="21" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>PUF_01</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>PUF_08</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>15.5625</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>48.6328125</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G26" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>249</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="27" ht="21" customHeight="1">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>PUF_01</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>PUF_09</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>17.3125</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>54.1015625</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="G27" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>277</v>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="28" ht="21" customHeight="1">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>PUF_01</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>PUF_10</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D28" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>46.875</v>
+      </c>
+      <c r="F28" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="I28" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="29" ht="21" customHeight="1">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>PUF_01</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>PUF_11</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D29" s="16" t="n">
+        <v>17.4375</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>54.4921875</v>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>279</v>
+      </c>
+      <c r="I29" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="30" ht="21" customHeight="1">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>PUF_01</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>PUF_12</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D30" s="16" t="n">
+        <v>17.375</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>54.296875</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G30" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>278</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="31" ht="21" customHeight="1">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>PUF_01</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>PUF_13</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D31" s="16" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>46.09375</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="G31" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H31" s="15" t="n">
+        <v>236</v>
+      </c>
+      <c r="I31" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="32" ht="21" customHeight="1">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>PUF_01</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>PUF_14</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D32" s="16" t="n">
+        <v>15.875</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>49.609375</v>
+      </c>
+      <c r="F32" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="G32" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>254</v>
+      </c>
+      <c r="I32" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="33" ht="21" customHeight="1">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>PUF_01</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>PUF_15</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D33" s="16" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>57.03125</v>
+      </c>
+      <c r="F33" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="G33" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>292</v>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="34" ht="21" customHeight="1">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>PUF_02</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>PUF_03</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D34" s="16" t="n">
+        <v>15.625</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>48.828125</v>
+      </c>
+      <c r="F34" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G34" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>250</v>
+      </c>
+      <c r="I34" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="35" ht="21" customHeight="1">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>PUF_02</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>PUF_04</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D35" s="16" t="n">
+        <v>16.1875</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>50.5859375</v>
+      </c>
+      <c r="F35" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G35" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>259</v>
+      </c>
+      <c r="I35" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="36" ht="21" customHeight="1">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>PUF_02</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>PUF_05</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D36" s="16" t="n">
+        <v>14.125</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>44.140625</v>
+      </c>
+      <c r="F36" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G36" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H36" s="15" t="n">
+        <v>226</v>
+      </c>
+      <c r="I36" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="37" ht="21" customHeight="1">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>PUF_02</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>PUF_06</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D37" s="16" t="n">
+        <v>14.1875</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>44.3359375</v>
+      </c>
+      <c r="F37" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G37" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="H37" s="15" t="n">
+        <v>227</v>
+      </c>
+      <c r="I37" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="38" ht="21" customHeight="1">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>PUF_02</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>PUF_07</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D38" s="16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>51.5625</v>
+      </c>
+      <c r="F38" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G38" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>264</v>
+      </c>
+      <c r="I38" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="39" ht="21" customHeight="1">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>PUF_02</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>PUF_08</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D39" s="16" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>52.34375</v>
+      </c>
+      <c r="F39" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="G39" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H39" s="15" t="n">
+        <v>268</v>
+      </c>
+      <c r="I39" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="40" ht="21" customHeight="1">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>PUF_02</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>PUF_09</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D40" s="16" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>47.65625</v>
+      </c>
+      <c r="F40" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G40" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H40" s="15" t="n">
+        <v>244</v>
+      </c>
+      <c r="I40" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="41" ht="21" customHeight="1">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>PUF_02</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>PUF_10</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>16.3125</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>50.9765625</v>
+      </c>
+      <c r="F41" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G41" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H41" s="15" t="n">
+        <v>261</v>
+      </c>
+      <c r="I41" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="42" ht="21" customHeight="1">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>PUF_02</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>PUF_11</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D42" s="16" t="n">
+        <v>15.375</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>48.046875</v>
+      </c>
+      <c r="F42" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G42" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H42" s="15" t="n">
+        <v>246</v>
+      </c>
+      <c r="I42" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="43" ht="21" customHeight="1">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>PUF_02</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>PUF_12</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D43" s="16" t="n">
+        <v>16.1875</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>50.5859375</v>
+      </c>
+      <c r="F43" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="G43" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="H43" s="15" t="n">
+        <v>259</v>
+      </c>
+      <c r="I43" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="44" ht="21" customHeight="1">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>PUF_02</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>PUF_13</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D44" s="16" t="n">
+        <v>15.9375</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>49.8046875</v>
+      </c>
+      <c r="F44" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G44" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H44" s="15" t="n">
+        <v>255</v>
+      </c>
+      <c r="I44" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="45" ht="21" customHeight="1">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>PUF_02</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>PUF_14</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D45" s="16" t="n">
+        <v>17.8125</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>55.6640625</v>
+      </c>
+      <c r="F45" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G45" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="H45" s="15" t="n">
+        <v>285</v>
+      </c>
+      <c r="I45" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="46" ht="21" customHeight="1">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>PUF_02</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>PUF_15</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D46" s="16" t="n">
+        <v>16.4375</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>51.3671875</v>
+      </c>
+      <c r="F46" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="G46" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>263</v>
+      </c>
+      <c r="I46" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="47" ht="21" customHeight="1">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>PUF_03</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>PUF_04</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D47" s="16" t="n">
+        <v>16.1875</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>50.5859375</v>
+      </c>
+      <c r="F47" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G47" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H47" s="15" t="n">
+        <v>259</v>
+      </c>
+      <c r="I47" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="48" ht="21" customHeight="1">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>PUF_03</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>PUF_05</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D48" s="16" t="n">
+        <v>17.625</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>55.078125</v>
+      </c>
+      <c r="F48" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G48" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>282</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="49" ht="21" customHeight="1">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>PUF_03</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>PUF_06</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D49" s="16" t="n">
+        <v>14.4375</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>45.1171875</v>
+      </c>
+      <c r="F49" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G49" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>231</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="50" ht="21" customHeight="1">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>PUF_03</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>PUF_07</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D50" s="16" t="n">
+        <v>14.625</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>45.703125</v>
+      </c>
+      <c r="F50" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G50" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>234</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="51" ht="21" customHeight="1">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>PUF_03</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>PUF_08</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D51" s="16" t="n">
+        <v>16.375</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>51.171875</v>
+      </c>
+      <c r="F51" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G51" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>262</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="52" ht="21" customHeight="1">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>PUF_03</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>PUF_09</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D52" s="16" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>49.21875</v>
+      </c>
+      <c r="F52" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G52" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>252</v>
+      </c>
+      <c r="I52" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="53" ht="21" customHeight="1">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>PUF_03</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>PUF_10</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D53" s="16" t="n">
+        <v>15.9375</v>
+      </c>
+      <c r="E53" s="17" t="n">
+        <v>49.8046875</v>
+      </c>
+      <c r="F53" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G53" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>255</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="54" ht="21" customHeight="1">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>PUF_03</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>PUF_11</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D54" s="16" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>50.78125</v>
+      </c>
+      <c r="F54" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G54" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>260</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="55" ht="21" customHeight="1">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>PUF_03</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>PUF_12</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D55" s="16" t="n">
+        <v>15.6875</v>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>49.0234375</v>
+      </c>
+      <c r="F55" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G55" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>251</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="56" ht="21" customHeight="1">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>PUF_03</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>PUF_13</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D56" s="16" t="n">
+        <v>15.9375</v>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>49.8046875</v>
+      </c>
+      <c r="F56" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G56" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H56" s="15" t="n">
+        <v>255</v>
+      </c>
+      <c r="I56" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="57" ht="21" customHeight="1">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>PUF_03</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>PUF_14</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D57" s="16" t="n">
+        <v>14.6875</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>45.8984375</v>
+      </c>
+      <c r="F57" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G57" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H57" s="15" t="n">
+        <v>235</v>
+      </c>
+      <c r="I57" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="58" ht="21" customHeight="1">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>PUF_03</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>PUF_15</t>
+        </is>
+      </c>
+      <c r="C58" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D58" s="16" t="n">
+        <v>13.9375</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>43.5546875</v>
+      </c>
+      <c r="F58" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G58" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H58" s="15" t="n">
+        <v>223</v>
+      </c>
+      <c r="I58" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="59" ht="21" customHeight="1">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>PUF_04</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>PUF_05</t>
+        </is>
+      </c>
+      <c r="C59" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D59" s="16" t="n">
+        <v>15.8125</v>
+      </c>
+      <c r="E59" s="17" t="n">
+        <v>49.4140625</v>
+      </c>
+      <c r="F59" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G59" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H59" s="15" t="n">
+        <v>253</v>
+      </c>
+      <c r="I59" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="60" ht="21" customHeight="1">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>PUF_04</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>PUF_06</t>
+        </is>
+      </c>
+      <c r="C60" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D60" s="16" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="E60" s="17" t="n">
+        <v>46.09375</v>
+      </c>
+      <c r="F60" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="G60" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H60" s="15" t="n">
+        <v>236</v>
+      </c>
+      <c r="I60" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="61" ht="21" customHeight="1">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>PUF_04</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>PUF_07</t>
+        </is>
+      </c>
+      <c r="C61" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D61" s="16" t="n">
+        <v>15.1875</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>47.4609375</v>
+      </c>
+      <c r="F61" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G61" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H61" s="15" t="n">
+        <v>243</v>
+      </c>
+      <c r="I61" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="62" ht="21" customHeight="1">
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>PUF_04</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>PUF_08</t>
+        </is>
+      </c>
+      <c r="C62" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D62" s="16" t="n">
+        <v>17.0625</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>53.3203125</v>
+      </c>
+      <c r="F62" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G62" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H62" s="15" t="n">
+        <v>273</v>
+      </c>
+      <c r="I62" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="63" ht="21" customHeight="1">
+      <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>PUF_04</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>PUF_09</t>
+        </is>
+      </c>
+      <c r="C63" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D63" s="16" t="n">
+        <v>14.8125</v>
+      </c>
+      <c r="E63" s="17" t="n">
+        <v>46.2890625</v>
+      </c>
+      <c r="F63" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G63" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="H63" s="15" t="n">
+        <v>237</v>
+      </c>
+      <c r="I63" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="64" ht="21" customHeight="1">
+      <c r="A64" s="14" t="inlineStr">
+        <is>
+          <t>PUF_04</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>PUF_10</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D64" s="16" t="n">
+        <v>15.875</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>49.609375</v>
+      </c>
+      <c r="F64" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G64" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H64" s="15" t="n">
+        <v>254</v>
+      </c>
+      <c r="I64" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="65" ht="21" customHeight="1">
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t>PUF_04</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>PUF_11</t>
+        </is>
+      </c>
+      <c r="C65" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D65" s="16" t="n">
+        <v>15.1875</v>
+      </c>
+      <c r="E65" s="17" t="n">
+        <v>47.4609375</v>
+      </c>
+      <c r="F65" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="G65" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H65" s="15" t="n">
+        <v>243</v>
+      </c>
+      <c r="I65" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="66" ht="21" customHeight="1">
+      <c r="A66" s="14" t="inlineStr">
+        <is>
+          <t>PUF_04</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>PUF_12</t>
+        </is>
+      </c>
+      <c r="C66" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D66" s="16" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="E66" s="17" t="n">
+        <v>50.78125</v>
+      </c>
+      <c r="F66" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G66" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H66" s="15" t="n">
+        <v>260</v>
+      </c>
+      <c r="I66" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="67" ht="21" customHeight="1">
+      <c r="A67" s="14" t="inlineStr">
+        <is>
+          <t>PUF_04</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>PUF_13</t>
+        </is>
+      </c>
+      <c r="C67" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D67" s="16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>48.4375</v>
+      </c>
+      <c r="F67" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G67" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H67" s="15" t="n">
+        <v>248</v>
+      </c>
+      <c r="I67" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="68" ht="21" customHeight="1">
+      <c r="A68" s="14" t="inlineStr">
+        <is>
+          <t>PUF_04</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>PUF_14</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D68" s="16" t="n">
+        <v>16.625</v>
+      </c>
+      <c r="E68" s="17" t="n">
+        <v>51.953125</v>
+      </c>
+      <c r="F68" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G68" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="H68" s="15" t="n">
+        <v>266</v>
+      </c>
+      <c r="I68" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="69" ht="21" customHeight="1">
+      <c r="A69" s="14" t="inlineStr">
+        <is>
+          <t>PUF_04</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>PUF_15</t>
+        </is>
+      </c>
+      <c r="C69" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D69" s="16" t="n">
+        <v>14.125</v>
+      </c>
+      <c r="E69" s="17" t="n">
+        <v>44.140625</v>
+      </c>
+      <c r="F69" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="G69" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="H69" s="15" t="n">
+        <v>226</v>
+      </c>
+      <c r="I69" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="70" ht="21" customHeight="1">
+      <c r="A70" s="14" t="inlineStr">
+        <is>
+          <t>PUF_05</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>PUF_06</t>
+        </is>
+      </c>
+      <c r="C70" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D70" s="16" t="n">
+        <v>15.4375</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>48.2421875</v>
+      </c>
+      <c r="F70" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G70" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H70" s="15" t="n">
+        <v>247</v>
+      </c>
+      <c r="I70" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="71" ht="21" customHeight="1">
+      <c r="A71" s="14" t="inlineStr">
+        <is>
+          <t>PUF_05</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>PUF_07</t>
+        </is>
+      </c>
+      <c r="C71" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D71" s="16" t="n">
+        <v>15.875</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>49.609375</v>
+      </c>
+      <c r="F71" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G71" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H71" s="15" t="n">
+        <v>254</v>
+      </c>
+      <c r="I71" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="72" ht="21" customHeight="1">
+      <c r="A72" s="14" t="inlineStr">
+        <is>
+          <t>PUF_05</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>PUF_08</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D72" s="16" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>47.265625</v>
+      </c>
+      <c r="F72" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G72" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H72" s="15" t="n">
+        <v>242</v>
+      </c>
+      <c r="I72" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="73" ht="21" customHeight="1">
+      <c r="A73" s="14" t="inlineStr">
+        <is>
+          <t>PUF_05</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>PUF_09</t>
+        </is>
+      </c>
+      <c r="C73" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D73" s="16" t="n">
+        <v>16.625</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>51.953125</v>
+      </c>
+      <c r="F73" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G73" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H73" s="15" t="n">
+        <v>266</v>
+      </c>
+      <c r="I73" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="74" ht="21" customHeight="1">
+      <c r="A74" s="14" t="inlineStr">
+        <is>
+          <t>PUF_05</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>PUF_10</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D74" s="16" t="n">
+        <v>14.9375</v>
+      </c>
+      <c r="E74" s="17" t="n">
+        <v>46.6796875</v>
+      </c>
+      <c r="F74" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G74" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H74" s="15" t="n">
+        <v>239</v>
+      </c>
+      <c r="I74" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="75" ht="21" customHeight="1">
+      <c r="A75" s="14" t="inlineStr">
+        <is>
+          <t>PUF_05</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>PUF_11</t>
+        </is>
+      </c>
+      <c r="C75" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D75" s="16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E75" s="17" t="n">
+        <v>54.6875</v>
+      </c>
+      <c r="F75" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G75" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="H75" s="15" t="n">
+        <v>280</v>
+      </c>
+      <c r="I75" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="76" ht="21" customHeight="1">
+      <c r="A76" s="14" t="inlineStr">
+        <is>
+          <t>PUF_05</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>PUF_12</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D76" s="16" t="n">
+        <v>16.8125</v>
+      </c>
+      <c r="E76" s="17" t="n">
+        <v>52.5390625</v>
+      </c>
+      <c r="F76" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G76" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="H76" s="15" t="n">
+        <v>269</v>
+      </c>
+      <c r="I76" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="77" ht="21" customHeight="1">
+      <c r="A77" s="14" t="inlineStr">
+        <is>
+          <t>PUF_05</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>PUF_13</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D77" s="16" t="n">
+        <v>15.1875</v>
+      </c>
+      <c r="E77" s="17" t="n">
+        <v>47.4609375</v>
+      </c>
+      <c r="F77" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G77" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H77" s="15" t="n">
+        <v>243</v>
+      </c>
+      <c r="I77" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="78" ht="21" customHeight="1">
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>PUF_05</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>PUF_14</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D78" s="16" t="n">
+        <v>17.0625</v>
+      </c>
+      <c r="E78" s="17" t="n">
+        <v>53.3203125</v>
+      </c>
+      <c r="F78" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="G78" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H78" s="15" t="n">
+        <v>273</v>
+      </c>
+      <c r="I78" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="79" ht="21" customHeight="1">
+      <c r="A79" s="14" t="inlineStr">
+        <is>
+          <t>PUF_05</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>PUF_15</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D79" s="16" t="n">
+        <v>17.4375</v>
+      </c>
+      <c r="E79" s="17" t="n">
+        <v>54.4921875</v>
+      </c>
+      <c r="F79" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G79" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="H79" s="15" t="n">
+        <v>279</v>
+      </c>
+      <c r="I79" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="80" ht="21" customHeight="1">
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>PUF_06</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>PUF_07</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D80" s="16" t="n">
+        <v>13.6875</v>
+      </c>
+      <c r="E80" s="17" t="n">
+        <v>42.7734375</v>
+      </c>
+      <c r="F80" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="G80" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="H80" s="15" t="n">
+        <v>219</v>
+      </c>
+      <c r="I80" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="81" ht="21" customHeight="1">
+      <c r="A81" s="14" t="inlineStr">
+        <is>
+          <t>PUF_06</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>PUF_08</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D81" s="16" t="n">
+        <v>17.8125</v>
+      </c>
+      <c r="E81" s="17" t="n">
+        <v>55.6640625</v>
+      </c>
+      <c r="F81" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G81" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="H81" s="15" t="n">
+        <v>285</v>
+      </c>
+      <c r="I81" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="82" ht="21" customHeight="1">
+      <c r="A82" s="14" t="inlineStr">
+        <is>
+          <t>PUF_06</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>PUF_09</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D82" s="16" t="n">
+        <v>15.3125</v>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>47.8515625</v>
+      </c>
+      <c r="F82" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G82" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H82" s="15" t="n">
+        <v>245</v>
+      </c>
+      <c r="I82" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="83" ht="21" customHeight="1">
+      <c r="A83" s="14" t="inlineStr">
+        <is>
+          <t>PUF_06</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>PUF_10</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D83" s="16" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="E83" s="17" t="n">
+        <v>50.78125</v>
+      </c>
+      <c r="F83" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="G83" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="H83" s="15" t="n">
+        <v>260</v>
+      </c>
+      <c r="I83" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="84" ht="21" customHeight="1">
+      <c r="A84" s="14" t="inlineStr">
+        <is>
+          <t>PUF_06</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>PUF_11</t>
+        </is>
+      </c>
+      <c r="C84" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D84" s="16" t="n">
+        <v>15.9375</v>
+      </c>
+      <c r="E84" s="17" t="n">
+        <v>49.8046875</v>
+      </c>
+      <c r="F84" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G84" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H84" s="15" t="n">
+        <v>255</v>
+      </c>
+      <c r="I84" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="85" ht="21" customHeight="1">
+      <c r="A85" s="14" t="inlineStr">
+        <is>
+          <t>PUF_06</t>
+        </is>
+      </c>
+      <c r="B85" s="14" t="inlineStr">
+        <is>
+          <t>PUF_12</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D85" s="16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E85" s="17" t="n">
+        <v>51.5625</v>
+      </c>
+      <c r="F85" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="G85" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H85" s="15" t="n">
+        <v>264</v>
+      </c>
+      <c r="I85" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="86" ht="21" customHeight="1">
+      <c r="A86" s="14" t="inlineStr">
+        <is>
+          <t>PUF_06</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>PUF_13</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D86" s="16" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="E86" s="17" t="n">
+        <v>49.21875</v>
+      </c>
+      <c r="F86" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G86" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H86" s="15" t="n">
+        <v>252</v>
+      </c>
+      <c r="I86" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="87" ht="21" customHeight="1">
+      <c r="A87" s="14" t="inlineStr">
+        <is>
+          <t>PUF_06</t>
+        </is>
+      </c>
+      <c r="B87" s="14" t="inlineStr">
+        <is>
+          <t>PUF_14</t>
+        </is>
+      </c>
+      <c r="C87" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D87" s="16" t="n">
+        <v>16.625</v>
+      </c>
+      <c r="E87" s="17" t="n">
+        <v>51.953125</v>
+      </c>
+      <c r="F87" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="G87" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H87" s="15" t="n">
+        <v>266</v>
+      </c>
+      <c r="I87" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="88" ht="21" customHeight="1">
+      <c r="A88" s="14" t="inlineStr">
+        <is>
+          <t>PUF_06</t>
+        </is>
+      </c>
+      <c r="B88" s="14" t="inlineStr">
+        <is>
+          <t>PUF_15</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D88" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="E88" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="F88" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G88" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H88" s="15" t="n">
+        <v>256</v>
+      </c>
+      <c r="I88" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="89" ht="21" customHeight="1">
+      <c r="A89" s="14" t="inlineStr">
+        <is>
+          <t>PUF_07</t>
+        </is>
+      </c>
+      <c r="B89" s="14" t="inlineStr">
+        <is>
+          <t>PUF_08</t>
+        </is>
+      </c>
+      <c r="C89" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D89" s="16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="E89" s="17" t="n">
+        <v>48.4375</v>
+      </c>
+      <c r="F89" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="G89" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H89" s="15" t="n">
+        <v>248</v>
+      </c>
+      <c r="I89" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="90" ht="21" customHeight="1">
+      <c r="A90" s="14" t="inlineStr">
+        <is>
+          <t>PUF_07</t>
+        </is>
+      </c>
+      <c r="B90" s="14" t="inlineStr">
+        <is>
+          <t>PUF_09</t>
+        </is>
+      </c>
+      <c r="C90" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D90" s="16" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="E90" s="17" t="n">
+        <v>47.265625</v>
+      </c>
+      <c r="F90" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="G90" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H90" s="15" t="n">
+        <v>242</v>
+      </c>
+      <c r="I90" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="91" ht="21" customHeight="1">
+      <c r="A91" s="14" t="inlineStr">
+        <is>
+          <t>PUF_07</t>
+        </is>
+      </c>
+      <c r="B91" s="14" t="inlineStr">
+        <is>
+          <t>PUF_10</t>
+        </is>
+      </c>
+      <c r="C91" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D91" s="16" t="n">
+        <v>14.8125</v>
+      </c>
+      <c r="E91" s="17" t="n">
+        <v>46.2890625</v>
+      </c>
+      <c r="F91" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G91" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H91" s="15" t="n">
+        <v>237</v>
+      </c>
+      <c r="I91" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="92" ht="21" customHeight="1">
+      <c r="A92" s="14" t="inlineStr">
+        <is>
+          <t>PUF_07</t>
+        </is>
+      </c>
+      <c r="B92" s="14" t="inlineStr">
+        <is>
+          <t>PUF_11</t>
+        </is>
+      </c>
+      <c r="C92" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D92" s="16" t="n">
+        <v>16.375</v>
+      </c>
+      <c r="E92" s="17" t="n">
+        <v>51.171875</v>
+      </c>
+      <c r="F92" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G92" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="H92" s="15" t="n">
+        <v>262</v>
+      </c>
+      <c r="I92" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="93" ht="21" customHeight="1">
+      <c r="A93" s="14" t="inlineStr">
+        <is>
+          <t>PUF_07</t>
+        </is>
+      </c>
+      <c r="B93" s="14" t="inlineStr">
+        <is>
+          <t>PUF_12</t>
+        </is>
+      </c>
+      <c r="C93" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D93" s="16" t="n">
+        <v>15.6875</v>
+      </c>
+      <c r="E93" s="17" t="n">
+        <v>49.0234375</v>
+      </c>
+      <c r="F93" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G93" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H93" s="15" t="n">
+        <v>251</v>
+      </c>
+      <c r="I93" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="94" ht="21" customHeight="1">
+      <c r="A94" s="14" t="inlineStr">
+        <is>
+          <t>PUF_07</t>
+        </is>
+      </c>
+      <c r="B94" s="14" t="inlineStr">
+        <is>
+          <t>PUF_13</t>
+        </is>
+      </c>
+      <c r="C94" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D94" s="16" t="n">
+        <v>16.0625</v>
+      </c>
+      <c r="E94" s="17" t="n">
+        <v>50.1953125</v>
+      </c>
+      <c r="F94" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G94" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H94" s="15" t="n">
+        <v>257</v>
+      </c>
+      <c r="I94" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="95" ht="21" customHeight="1">
+      <c r="A95" s="14" t="inlineStr">
+        <is>
+          <t>PUF_07</t>
+        </is>
+      </c>
+      <c r="B95" s="14" t="inlineStr">
+        <is>
+          <t>PUF_14</t>
+        </is>
+      </c>
+      <c r="C95" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D95" s="16" t="n">
+        <v>16.8125</v>
+      </c>
+      <c r="E95" s="17" t="n">
+        <v>52.5390625</v>
+      </c>
+      <c r="F95" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G95" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="H95" s="15" t="n">
+        <v>269</v>
+      </c>
+      <c r="I95" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="96" ht="21" customHeight="1">
+      <c r="A96" s="14" t="inlineStr">
+        <is>
+          <t>PUF_07</t>
+        </is>
+      </c>
+      <c r="B96" s="14" t="inlineStr">
+        <is>
+          <t>PUF_15</t>
+        </is>
+      </c>
+      <c r="C96" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D96" s="16" t="n">
+        <v>13.1875</v>
+      </c>
+      <c r="E96" s="17" t="n">
+        <v>41.2109375</v>
+      </c>
+      <c r="F96" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="G96" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="H96" s="15" t="n">
+        <v>211</v>
+      </c>
+      <c r="I96" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="97" ht="21" customHeight="1">
+      <c r="A97" s="14" t="inlineStr">
+        <is>
+          <t>PUF_08</t>
+        </is>
+      </c>
+      <c r="B97" s="14" t="inlineStr">
+        <is>
+          <t>PUF_09</t>
+        </is>
+      </c>
+      <c r="C97" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D97" s="16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E97" s="17" t="n">
+        <v>51.5625</v>
+      </c>
+      <c r="F97" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G97" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H97" s="15" t="n">
+        <v>264</v>
+      </c>
+      <c r="I97" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="98" ht="21" customHeight="1">
+      <c r="A98" s="14" t="inlineStr">
+        <is>
+          <t>PUF_08</t>
+        </is>
+      </c>
+      <c r="B98" s="14" t="inlineStr">
+        <is>
+          <t>PUF_10</t>
+        </is>
+      </c>
+      <c r="C98" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D98" s="16" t="n">
+        <v>16.6875</v>
+      </c>
+      <c r="E98" s="17" t="n">
+        <v>52.1484375</v>
+      </c>
+      <c r="F98" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="G98" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H98" s="15" t="n">
+        <v>267</v>
+      </c>
+      <c r="I98" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="99" ht="21" customHeight="1">
+      <c r="A99" s="14" t="inlineStr">
+        <is>
+          <t>PUF_08</t>
+        </is>
+      </c>
+      <c r="B99" s="14" t="inlineStr">
+        <is>
+          <t>PUF_11</t>
+        </is>
+      </c>
+      <c r="C99" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D99" s="16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E99" s="17" t="n">
+        <v>51.5625</v>
+      </c>
+      <c r="F99" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G99" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H99" s="15" t="n">
+        <v>264</v>
+      </c>
+      <c r="I99" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="100" ht="21" customHeight="1">
+      <c r="A100" s="14" t="inlineStr">
+        <is>
+          <t>PUF_08</t>
+        </is>
+      </c>
+      <c r="B100" s="14" t="inlineStr">
+        <is>
+          <t>PUF_12</t>
+        </is>
+      </c>
+      <c r="C100" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D100" s="16" t="n">
+        <v>16.3125</v>
+      </c>
+      <c r="E100" s="17" t="n">
+        <v>50.9765625</v>
+      </c>
+      <c r="F100" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G100" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H100" s="15" t="n">
+        <v>261</v>
+      </c>
+      <c r="I100" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="101" ht="21" customHeight="1">
+      <c r="A101" s="14" t="inlineStr">
+        <is>
+          <t>PUF_08</t>
+        </is>
+      </c>
+      <c r="B101" s="14" t="inlineStr">
+        <is>
+          <t>PUF_13</t>
+        </is>
+      </c>
+      <c r="C101" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D101" s="16" t="n">
+        <v>16.6875</v>
+      </c>
+      <c r="E101" s="17" t="n">
+        <v>52.1484375</v>
+      </c>
+      <c r="F101" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G101" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H101" s="15" t="n">
+        <v>267</v>
+      </c>
+      <c r="I101" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="102" ht="21" customHeight="1">
+      <c r="A102" s="14" t="inlineStr">
+        <is>
+          <t>PUF_08</t>
+        </is>
+      </c>
+      <c r="B102" s="14" t="inlineStr">
+        <is>
+          <t>PUF_14</t>
+        </is>
+      </c>
+      <c r="C102" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D102" s="16" t="n">
+        <v>15.3125</v>
+      </c>
+      <c r="E102" s="17" t="n">
+        <v>47.8515625</v>
+      </c>
+      <c r="F102" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G102" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="H102" s="15" t="n">
+        <v>245</v>
+      </c>
+      <c r="I102" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="103" ht="21" customHeight="1">
+      <c r="A103" s="14" t="inlineStr">
+        <is>
+          <t>PUF_08</t>
+        </is>
+      </c>
+      <c r="B103" s="14" t="inlineStr">
+        <is>
+          <t>PUF_15</t>
+        </is>
+      </c>
+      <c r="C103" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D103" s="16" t="n">
+        <v>15.3125</v>
+      </c>
+      <c r="E103" s="17" t="n">
+        <v>47.8515625</v>
+      </c>
+      <c r="F103" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G103" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H103" s="15" t="n">
+        <v>245</v>
+      </c>
+      <c r="I103" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="104" ht="21" customHeight="1">
+      <c r="A104" s="14" t="inlineStr">
+        <is>
+          <t>PUF_09</t>
+        </is>
+      </c>
+      <c r="B104" s="14" t="inlineStr">
+        <is>
+          <t>PUF_10</t>
+        </is>
+      </c>
+      <c r="C104" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D104" s="16" t="n">
+        <v>15.4375</v>
+      </c>
+      <c r="E104" s="17" t="n">
+        <v>48.2421875</v>
+      </c>
+      <c r="F104" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G104" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H104" s="15" t="n">
+        <v>247</v>
+      </c>
+      <c r="I104" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="105" ht="21" customHeight="1">
+      <c r="A105" s="14" t="inlineStr">
+        <is>
+          <t>PUF_09</t>
+        </is>
+      </c>
+      <c r="B105" s="14" t="inlineStr">
+        <is>
+          <t>PUF_11</t>
+        </is>
+      </c>
+      <c r="C105" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D105" s="16" t="n">
+        <v>14.625</v>
+      </c>
+      <c r="E105" s="17" t="n">
+        <v>45.703125</v>
+      </c>
+      <c r="F105" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G105" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="H105" s="15" t="n">
+        <v>234</v>
+      </c>
+      <c r="I105" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="106" ht="21" customHeight="1">
+      <c r="A106" s="14" t="inlineStr">
+        <is>
+          <t>PUF_09</t>
+        </is>
+      </c>
+      <c r="B106" s="14" t="inlineStr">
+        <is>
+          <t>PUF_12</t>
+        </is>
+      </c>
+      <c r="C106" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D106" s="16" t="n">
+        <v>16.5625</v>
+      </c>
+      <c r="E106" s="17" t="n">
+        <v>51.7578125</v>
+      </c>
+      <c r="F106" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G106" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="H106" s="15" t="n">
+        <v>265</v>
+      </c>
+      <c r="I106" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="107" ht="21" customHeight="1">
+      <c r="A107" s="14" t="inlineStr">
+        <is>
+          <t>PUF_09</t>
+        </is>
+      </c>
+      <c r="B107" s="14" t="inlineStr">
+        <is>
+          <t>PUF_13</t>
+        </is>
+      </c>
+      <c r="C107" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D107" s="16" t="n">
+        <v>14.9375</v>
+      </c>
+      <c r="E107" s="17" t="n">
+        <v>46.6796875</v>
+      </c>
+      <c r="F107" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G107" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H107" s="15" t="n">
+        <v>239</v>
+      </c>
+      <c r="I107" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="108" ht="21" customHeight="1">
+      <c r="A108" s="14" t="inlineStr">
+        <is>
+          <t>PUF_09</t>
+        </is>
+      </c>
+      <c r="B108" s="14" t="inlineStr">
+        <is>
+          <t>PUF_14</t>
+        </is>
+      </c>
+      <c r="C108" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D108" s="16" t="n">
+        <v>15.1875</v>
+      </c>
+      <c r="E108" s="17" t="n">
+        <v>47.4609375</v>
+      </c>
+      <c r="F108" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G108" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H108" s="15" t="n">
+        <v>243</v>
+      </c>
+      <c r="I108" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="109" ht="21" customHeight="1">
+      <c r="A109" s="14" t="inlineStr">
+        <is>
+          <t>PUF_09</t>
+        </is>
+      </c>
+      <c r="B109" s="14" t="inlineStr">
+        <is>
+          <t>PUF_15</t>
+        </is>
+      </c>
+      <c r="C109" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D109" s="16" t="n">
+        <v>15.8125</v>
+      </c>
+      <c r="E109" s="17" t="n">
+        <v>49.4140625</v>
+      </c>
+      <c r="F109" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G109" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H109" s="15" t="n">
+        <v>253</v>
+      </c>
+      <c r="I109" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="110" ht="21" customHeight="1">
+      <c r="A110" s="14" t="inlineStr">
+        <is>
+          <t>PUF_10</t>
+        </is>
+      </c>
+      <c r="B110" s="14" t="inlineStr">
+        <is>
+          <t>PUF_11</t>
+        </is>
+      </c>
+      <c r="C110" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D110" s="16" t="n">
+        <v>16.0625</v>
+      </c>
+      <c r="E110" s="17" t="n">
+        <v>50.1953125</v>
+      </c>
+      <c r="F110" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G110" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H110" s="15" t="n">
+        <v>257</v>
+      </c>
+      <c r="I110" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="111" ht="21" customHeight="1">
+      <c r="A111" s="14" t="inlineStr">
+        <is>
+          <t>PUF_10</t>
+        </is>
+      </c>
+      <c r="B111" s="14" t="inlineStr">
+        <is>
+          <t>PUF_12</t>
+        </is>
+      </c>
+      <c r="C111" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D111" s="16" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="E111" s="17" t="n">
+        <v>47.265625</v>
+      </c>
+      <c r="F111" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="G111" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="H111" s="15" t="n">
+        <v>242</v>
+      </c>
+      <c r="I111" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="112" ht="21" customHeight="1">
+      <c r="A112" s="14" t="inlineStr">
+        <is>
+          <t>PUF_10</t>
+        </is>
+      </c>
+      <c r="B112" s="14" t="inlineStr">
+        <is>
+          <t>PUF_13</t>
+        </is>
+      </c>
+      <c r="C112" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D112" s="16" t="n">
+        <v>15.125</v>
+      </c>
+      <c r="E112" s="17" t="n">
+        <v>47.265625</v>
+      </c>
+      <c r="F112" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G112" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H112" s="15" t="n">
+        <v>242</v>
+      </c>
+      <c r="I112" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="113" ht="21" customHeight="1">
+      <c r="A113" s="14" t="inlineStr">
+        <is>
+          <t>PUF_10</t>
+        </is>
+      </c>
+      <c r="B113" s="14" t="inlineStr">
+        <is>
+          <t>PUF_14</t>
+        </is>
+      </c>
+      <c r="C113" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D113" s="16" t="n">
+        <v>15.625</v>
+      </c>
+      <c r="E113" s="17" t="n">
+        <v>48.828125</v>
+      </c>
+      <c r="F113" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G113" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H113" s="15" t="n">
+        <v>250</v>
+      </c>
+      <c r="I113" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="114" ht="21" customHeight="1">
+      <c r="A114" s="14" t="inlineStr">
+        <is>
+          <t>PUF_10</t>
+        </is>
+      </c>
+      <c r="B114" s="14" t="inlineStr">
+        <is>
+          <t>PUF_15</t>
+        </is>
+      </c>
+      <c r="C114" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D114" s="16" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="E114" s="17" t="n">
+        <v>50.78125</v>
+      </c>
+      <c r="F114" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G114" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H114" s="15" t="n">
+        <v>260</v>
+      </c>
+      <c r="I114" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="115" ht="21" customHeight="1">
+      <c r="A115" s="14" t="inlineStr">
+        <is>
+          <t>PUF_11</t>
+        </is>
+      </c>
+      <c r="B115" s="14" t="inlineStr">
+        <is>
+          <t>PUF_12</t>
+        </is>
+      </c>
+      <c r="C115" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D115" s="16" t="n">
+        <v>15.0625</v>
+      </c>
+      <c r="E115" s="17" t="n">
+        <v>47.0703125</v>
+      </c>
+      <c r="F115" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G115" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="H115" s="15" t="n">
+        <v>241</v>
+      </c>
+      <c r="I115" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="116" ht="21" customHeight="1">
+      <c r="A116" s="14" t="inlineStr">
+        <is>
+          <t>PUF_11</t>
+        </is>
+      </c>
+      <c r="B116" s="14" t="inlineStr">
+        <is>
+          <t>PUF_13</t>
+        </is>
+      </c>
+      <c r="C116" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D116" s="16" t="n">
+        <v>15.8125</v>
+      </c>
+      <c r="E116" s="17" t="n">
+        <v>49.4140625</v>
+      </c>
+      <c r="F116" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G116" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="H116" s="15" t="n">
+        <v>253</v>
+      </c>
+      <c r="I116" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="117" ht="21" customHeight="1">
+      <c r="A117" s="14" t="inlineStr">
+        <is>
+          <t>PUF_11</t>
+        </is>
+      </c>
+      <c r="B117" s="14" t="inlineStr">
+        <is>
+          <t>PUF_14</t>
+        </is>
+      </c>
+      <c r="C117" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D117" s="16" t="n">
+        <v>15.0625</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>47.0703125</v>
+      </c>
+      <c r="F117" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G117" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="H117" s="15" t="n">
+        <v>241</v>
+      </c>
+      <c r="I117" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="118" ht="21" customHeight="1">
+      <c r="A118" s="14" t="inlineStr">
+        <is>
+          <t>PUF_11</t>
+        </is>
+      </c>
+      <c r="B118" s="14" t="inlineStr">
+        <is>
+          <t>PUF_15</t>
+        </is>
+      </c>
+      <c r="C118" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D118" s="16" t="n">
+        <v>15.8125</v>
+      </c>
+      <c r="E118" s="17" t="n">
+        <v>49.4140625</v>
+      </c>
+      <c r="F118" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="G118" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H118" s="15" t="n">
+        <v>253</v>
+      </c>
+      <c r="I118" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="119" ht="21" customHeight="1">
+      <c r="A119" s="14" t="inlineStr">
+        <is>
+          <t>PUF_12</t>
+        </is>
+      </c>
+      <c r="B119" s="14" t="inlineStr">
+        <is>
+          <t>PUF_13</t>
+        </is>
+      </c>
+      <c r="C119" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D119" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="E119" s="17" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="F119" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G119" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="H119" s="15" t="n">
+        <v>288</v>
+      </c>
+      <c r="I119" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="120" ht="21" customHeight="1">
+      <c r="A120" s="14" t="inlineStr">
+        <is>
+          <t>PUF_12</t>
+        </is>
+      </c>
+      <c r="B120" s="14" t="inlineStr">
+        <is>
+          <t>PUF_14</t>
+        </is>
+      </c>
+      <c r="C120" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D120" s="16" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="E120" s="17" t="n">
+        <v>47.65625</v>
+      </c>
+      <c r="F120" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G120" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H120" s="15" t="n">
+        <v>244</v>
+      </c>
+      <c r="I120" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="121" ht="21" customHeight="1">
+      <c r="A121" s="14" t="inlineStr">
+        <is>
+          <t>PUF_12</t>
+        </is>
+      </c>
+      <c r="B121" s="14" t="inlineStr">
+        <is>
+          <t>PUF_15</t>
+        </is>
+      </c>
+      <c r="C121" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D121" s="16" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="E121" s="17" t="n">
+        <v>42.96875</v>
+      </c>
+      <c r="F121" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G121" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="H121" s="15" t="n">
+        <v>220</v>
+      </c>
+      <c r="I121" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="122" ht="21" customHeight="1">
+      <c r="A122" s="14" t="inlineStr">
+        <is>
+          <t>PUF_13</t>
+        </is>
+      </c>
+      <c r="B122" s="14" t="inlineStr">
+        <is>
+          <t>PUF_14</t>
+        </is>
+      </c>
+      <c r="C122" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D122" s="16" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="E122" s="17" t="n">
+        <v>49.21875</v>
+      </c>
+      <c r="F122" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G122" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H122" s="15" t="n">
+        <v>252</v>
+      </c>
+      <c r="I122" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="123" ht="21" customHeight="1">
+      <c r="A123" s="14" t="inlineStr">
+        <is>
+          <t>PUF_13</t>
+        </is>
+      </c>
+      <c r="B123" s="14" t="inlineStr">
+        <is>
+          <t>PUF_15</t>
+        </is>
+      </c>
+      <c r="C123" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D123" s="16" t="n">
+        <v>15.875</v>
+      </c>
+      <c r="E123" s="17" t="n">
+        <v>49.609375</v>
+      </c>
+      <c r="F123" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G123" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H123" s="15" t="n">
+        <v>254</v>
+      </c>
+      <c r="I123" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="124" ht="21" customHeight="1">
+      <c r="A124" s="14" t="inlineStr">
+        <is>
+          <t>PUF_14</t>
+        </is>
+      </c>
+      <c r="B124" s="14" t="inlineStr">
+        <is>
+          <t>PUF_15</t>
+        </is>
+      </c>
+      <c r="C124" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D124" s="16" t="n">
+        <v>15.625</v>
+      </c>
+      <c r="E124" s="17" t="n">
+        <v>48.828125</v>
+      </c>
+      <c r="F124" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="G124" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H124" s="15" t="n">
+        <v>250</v>
+      </c>
+      <c r="I124" s="15" t="n">
+        <v>512</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Multi-chip mean Hamming distance matrix (%)</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="n"/>
+      <c r="C1" s="7" t="n"/>
+      <c r="D1" s="7" t="n"/>
+      <c r="E1" s="7" t="n"/>
+      <c r="F1" s="7" t="n"/>
+      <c r="G1" s="7" t="n"/>
+      <c r="H1" s="7" t="n"/>
+      <c r="I1" s="7" t="n"/>
+      <c r="J1" s="7" t="n"/>
+      <c r="K1" s="7" t="n"/>
+      <c r="L1" s="7" t="n"/>
+      <c r="M1" s="7" t="n"/>
+      <c r="N1" s="7" t="n"/>
+      <c r="O1" s="7" t="n"/>
+      <c r="P1" s="7" t="n"/>
+      <c r="Q1" s="7" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Each off-diagonal value is the mean HD percentage over 16 matched challenges; diagonal self-comparisons are 0%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>PUF_00</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>PUF_01</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>PUF_02</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>PUF_03</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>PUF_04</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>PUF_05</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>PUF_06</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>PUF_07</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>PUF_08</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>PUF_09</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>PUF_10</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>PUF_11</t>
+        </is>
+      </c>
+      <c r="N4" s="13" t="inlineStr">
+        <is>
+          <t>PUF_12</t>
+        </is>
+      </c>
+      <c r="O4" s="13" t="inlineStr">
+        <is>
+          <t>PUF_13</t>
+        </is>
+      </c>
+      <c r="P4" s="13" t="inlineStr">
+        <is>
+          <t>PUF_14</t>
+        </is>
+      </c>
+      <c r="Q4" s="13" t="inlineStr">
+        <is>
+          <t>PUF_15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>PUF_00</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>48.046875</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>50.1953125</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>49.0234375</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>46.09375</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>52.9296875</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>48.828125</v>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>48.6328125</v>
+      </c>
+      <c r="J5" s="17" t="n">
+        <v>55.2734375</v>
+      </c>
+      <c r="K5" s="17" t="n">
+        <v>44.7265625</v>
+      </c>
+      <c r="L5" s="17" t="n">
+        <v>48.4375</v>
+      </c>
+      <c r="M5" s="17" t="n">
+        <v>49.8046875</v>
+      </c>
+      <c r="N5" s="17" t="n">
+        <v>50.390625</v>
+      </c>
+      <c r="O5" s="17" t="n">
+        <v>49.21875</v>
+      </c>
+      <c r="P5" s="17" t="n">
+        <v>42.578125</v>
+      </c>
+      <c r="Q5" s="17" t="n">
+        <v>49.21875</v>
+      </c>
+    </row>
+    <row r="6" ht="21" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>PUF_01</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>48.046875</v>
+      </c>
+      <c r="C6" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>46.2890625</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>49.8046875</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>49.609375</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>47.0703125</v>
+      </c>
+      <c r="H6" s="17" t="n">
+        <v>51.5625</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>48.2421875</v>
+      </c>
+      <c r="J6" s="17" t="n">
+        <v>48.6328125</v>
+      </c>
+      <c r="K6" s="17" t="n">
+        <v>54.1015625</v>
+      </c>
+      <c r="L6" s="17" t="n">
+        <v>46.875</v>
+      </c>
+      <c r="M6" s="17" t="n">
+        <v>54.4921875</v>
+      </c>
+      <c r="N6" s="17" t="n">
+        <v>54.296875</v>
+      </c>
+      <c r="O6" s="17" t="n">
+        <v>46.09375</v>
+      </c>
+      <c r="P6" s="17" t="n">
+        <v>49.609375</v>
+      </c>
+      <c r="Q6" s="17" t="n">
+        <v>57.03125</v>
+      </c>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>PUF_02</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>50.1953125</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>46.2890625</v>
+      </c>
+      <c r="D7" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>48.828125</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>50.5859375</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>44.140625</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>44.3359375</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>51.5625</v>
+      </c>
+      <c r="J7" s="17" t="n">
+        <v>52.34375</v>
+      </c>
+      <c r="K7" s="17" t="n">
+        <v>47.65625</v>
+      </c>
+      <c r="L7" s="17" t="n">
+        <v>50.9765625</v>
+      </c>
+      <c r="M7" s="17" t="n">
+        <v>48.046875</v>
+      </c>
+      <c r="N7" s="17" t="n">
+        <v>50.5859375</v>
+      </c>
+      <c r="O7" s="17" t="n">
+        <v>49.8046875</v>
+      </c>
+      <c r="P7" s="17" t="n">
+        <v>55.6640625</v>
+      </c>
+      <c r="Q7" s="17" t="n">
+        <v>51.3671875</v>
+      </c>
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>PUF_03</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n">
+        <v>49.0234375</v>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>49.8046875</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>48.828125</v>
+      </c>
+      <c r="E8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>50.5859375</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>55.078125</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>45.1171875</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>45.703125</v>
+      </c>
+      <c r="J8" s="17" t="n">
+        <v>51.171875</v>
+      </c>
+      <c r="K8" s="17" t="n">
+        <v>49.21875</v>
+      </c>
+      <c r="L8" s="17" t="n">
+        <v>49.8046875</v>
+      </c>
+      <c r="M8" s="17" t="n">
+        <v>50.78125</v>
+      </c>
+      <c r="N8" s="17" t="n">
+        <v>49.0234375</v>
+      </c>
+      <c r="O8" s="17" t="n">
+        <v>49.8046875</v>
+      </c>
+      <c r="P8" s="17" t="n">
+        <v>45.8984375</v>
+      </c>
+      <c r="Q8" s="17" t="n">
+        <v>43.5546875</v>
+      </c>
+    </row>
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>PUF_04</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n">
+        <v>46.09375</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>49.609375</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>50.5859375</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>50.5859375</v>
+      </c>
+      <c r="F9" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>49.4140625</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>46.09375</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>47.4609375</v>
+      </c>
+      <c r="J9" s="17" t="n">
+        <v>53.3203125</v>
+      </c>
+      <c r="K9" s="17" t="n">
+        <v>46.2890625</v>
+      </c>
+      <c r="L9" s="17" t="n">
+        <v>49.609375</v>
+      </c>
+      <c r="M9" s="17" t="n">
+        <v>47.4609375</v>
+      </c>
+      <c r="N9" s="17" t="n">
+        <v>50.78125</v>
+      </c>
+      <c r="O9" s="17" t="n">
+        <v>48.4375</v>
+      </c>
+      <c r="P9" s="17" t="n">
+        <v>51.953125</v>
+      </c>
+      <c r="Q9" s="17" t="n">
+        <v>44.140625</v>
+      </c>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>PUF_05</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n">
+        <v>52.9296875</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>47.0703125</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>44.140625</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>55.078125</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>49.4140625</v>
+      </c>
+      <c r="G10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>48.2421875</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>49.609375</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>47.265625</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>51.953125</v>
+      </c>
+      <c r="L10" s="17" t="n">
+        <v>46.6796875</v>
+      </c>
+      <c r="M10" s="17" t="n">
+        <v>54.6875</v>
+      </c>
+      <c r="N10" s="17" t="n">
+        <v>52.5390625</v>
+      </c>
+      <c r="O10" s="17" t="n">
+        <v>47.4609375</v>
+      </c>
+      <c r="P10" s="17" t="n">
+        <v>53.3203125</v>
+      </c>
+      <c r="Q10" s="17" t="n">
+        <v>54.4921875</v>
+      </c>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>PUF_06</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>48.828125</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>51.5625</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>44.3359375</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>45.1171875</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>46.09375</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>48.2421875</v>
+      </c>
+      <c r="H11" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>42.7734375</v>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>55.6640625</v>
+      </c>
+      <c r="K11" s="17" t="n">
+        <v>47.8515625</v>
+      </c>
+      <c r="L11" s="17" t="n">
+        <v>50.78125</v>
+      </c>
+      <c r="M11" s="17" t="n">
+        <v>49.8046875</v>
+      </c>
+      <c r="N11" s="17" t="n">
+        <v>51.5625</v>
+      </c>
+      <c r="O11" s="17" t="n">
+        <v>49.21875</v>
+      </c>
+      <c r="P11" s="17" t="n">
+        <v>51.953125</v>
+      </c>
+      <c r="Q11" s="17" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" ht="21" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>PUF_07</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n">
+        <v>48.6328125</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>48.2421875</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>51.5625</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>45.703125</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>47.4609375</v>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>49.609375</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>42.7734375</v>
+      </c>
+      <c r="I12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>48.4375</v>
+      </c>
+      <c r="K12" s="17" t="n">
+        <v>47.265625</v>
+      </c>
+      <c r="L12" s="17" t="n">
+        <v>46.2890625</v>
+      </c>
+      <c r="M12" s="17" t="n">
+        <v>51.171875</v>
+      </c>
+      <c r="N12" s="17" t="n">
+        <v>49.0234375</v>
+      </c>
+      <c r="O12" s="17" t="n">
+        <v>50.1953125</v>
+      </c>
+      <c r="P12" s="17" t="n">
+        <v>52.5390625</v>
+      </c>
+      <c r="Q12" s="17" t="n">
+        <v>41.2109375</v>
+      </c>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>PUF_08</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>55.2734375</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>48.6328125</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>52.34375</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>51.171875</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>53.3203125</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>47.265625</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>55.6640625</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>48.4375</v>
+      </c>
+      <c r="J13" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="17" t="n">
+        <v>51.5625</v>
+      </c>
+      <c r="L13" s="17" t="n">
+        <v>52.1484375</v>
+      </c>
+      <c r="M13" s="17" t="n">
+        <v>51.5625</v>
+      </c>
+      <c r="N13" s="17" t="n">
+        <v>50.9765625</v>
+      </c>
+      <c r="O13" s="17" t="n">
+        <v>52.1484375</v>
+      </c>
+      <c r="P13" s="17" t="n">
+        <v>47.8515625</v>
+      </c>
+      <c r="Q13" s="17" t="n">
+        <v>47.8515625</v>
+      </c>
+    </row>
+    <row r="14" ht="21" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>PUF_09</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>44.7265625</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>54.1015625</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>47.65625</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>49.21875</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>46.2890625</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>51.953125</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>47.8515625</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>47.265625</v>
+      </c>
+      <c r="J14" s="17" t="n">
+        <v>51.5625</v>
+      </c>
+      <c r="K14" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="17" t="n">
+        <v>48.2421875</v>
+      </c>
+      <c r="M14" s="17" t="n">
+        <v>45.703125</v>
+      </c>
+      <c r="N14" s="17" t="n">
+        <v>51.7578125</v>
+      </c>
+      <c r="O14" s="17" t="n">
+        <v>46.6796875</v>
+      </c>
+      <c r="P14" s="17" t="n">
+        <v>47.4609375</v>
+      </c>
+      <c r="Q14" s="17" t="n">
+        <v>49.4140625</v>
+      </c>
+    </row>
+    <row r="15" ht="21" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>PUF_10</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>48.4375</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>46.875</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>50.9765625</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>49.8046875</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>49.609375</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>46.6796875</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>50.78125</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>46.2890625</v>
+      </c>
+      <c r="J15" s="17" t="n">
+        <v>52.1484375</v>
+      </c>
+      <c r="K15" s="17" t="n">
+        <v>48.2421875</v>
+      </c>
+      <c r="L15" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="17" t="n">
+        <v>50.1953125</v>
+      </c>
+      <c r="N15" s="17" t="n">
+        <v>47.265625</v>
+      </c>
+      <c r="O15" s="17" t="n">
+        <v>47.265625</v>
+      </c>
+      <c r="P15" s="17" t="n">
+        <v>48.828125</v>
+      </c>
+      <c r="Q15" s="17" t="n">
+        <v>50.78125</v>
+      </c>
+    </row>
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>PUF_11</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>49.8046875</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>54.4921875</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>48.046875</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>50.78125</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>47.4609375</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>54.6875</v>
+      </c>
+      <c r="H16" s="17" t="n">
+        <v>49.8046875</v>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>51.171875</v>
+      </c>
+      <c r="J16" s="17" t="n">
+        <v>51.5625</v>
+      </c>
+      <c r="K16" s="17" t="n">
+        <v>45.703125</v>
+      </c>
+      <c r="L16" s="17" t="n">
+        <v>50.1953125</v>
+      </c>
+      <c r="M16" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="17" t="n">
+        <v>47.0703125</v>
+      </c>
+      <c r="O16" s="17" t="n">
+        <v>49.4140625</v>
+      </c>
+      <c r="P16" s="17" t="n">
+        <v>47.0703125</v>
+      </c>
+      <c r="Q16" s="17" t="n">
+        <v>49.4140625</v>
+      </c>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>PUF_12</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>50.390625</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>54.296875</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>50.5859375</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>49.0234375</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>50.78125</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <v>52.5390625</v>
+      </c>
+      <c r="H17" s="17" t="n">
+        <v>51.5625</v>
+      </c>
+      <c r="I17" s="17" t="n">
+        <v>49.0234375</v>
+      </c>
+      <c r="J17" s="17" t="n">
+        <v>50.9765625</v>
+      </c>
+      <c r="K17" s="17" t="n">
+        <v>51.7578125</v>
+      </c>
+      <c r="L17" s="17" t="n">
+        <v>47.265625</v>
+      </c>
+      <c r="M17" s="17" t="n">
+        <v>47.0703125</v>
+      </c>
+      <c r="N17" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="17" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="P17" s="17" t="n">
+        <v>47.65625</v>
+      </c>
+      <c r="Q17" s="17" t="n">
+        <v>42.96875</v>
+      </c>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>PUF_13</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>49.21875</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>46.09375</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>49.8046875</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>49.8046875</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>48.4375</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <v>47.4609375</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>49.21875</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <v>50.1953125</v>
+      </c>
+      <c r="J18" s="17" t="n">
+        <v>52.1484375</v>
+      </c>
+      <c r="K18" s="17" t="n">
+        <v>46.6796875</v>
+      </c>
+      <c r="L18" s="17" t="n">
+        <v>47.265625</v>
+      </c>
+      <c r="M18" s="17" t="n">
+        <v>49.4140625</v>
+      </c>
+      <c r="N18" s="17" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="O18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="17" t="n">
+        <v>49.21875</v>
+      </c>
+      <c r="Q18" s="17" t="n">
+        <v>49.609375</v>
+      </c>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>PUF_14</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>42.578125</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>49.609375</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>55.6640625</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>45.8984375</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>51.953125</v>
+      </c>
+      <c r="G19" s="17" t="n">
+        <v>53.3203125</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>51.953125</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>52.5390625</v>
+      </c>
+      <c r="J19" s="17" t="n">
+        <v>47.8515625</v>
+      </c>
+      <c r="K19" s="17" t="n">
+        <v>47.4609375</v>
+      </c>
+      <c r="L19" s="17" t="n">
+        <v>48.828125</v>
+      </c>
+      <c r="M19" s="17" t="n">
+        <v>47.0703125</v>
+      </c>
+      <c r="N19" s="17" t="n">
+        <v>47.65625</v>
+      </c>
+      <c r="O19" s="17" t="n">
+        <v>49.21875</v>
+      </c>
+      <c r="P19" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="17" t="n">
+        <v>48.828125</v>
+      </c>
+    </row>
+    <row r="20" ht="21" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>PUF_15</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n">
+        <v>49.21875</v>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>57.03125</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>51.3671875</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>43.5546875</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>44.140625</v>
+      </c>
+      <c r="G20" s="17" t="n">
+        <v>54.4921875</v>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>41.2109375</v>
+      </c>
+      <c r="J20" s="17" t="n">
+        <v>47.8515625</v>
+      </c>
+      <c r="K20" s="17" t="n">
+        <v>49.4140625</v>
+      </c>
+      <c r="L20" s="17" t="n">
+        <v>50.78125</v>
+      </c>
+      <c r="M20" s="17" t="n">
+        <v>49.4140625</v>
+      </c>
+      <c r="N20" s="17" t="n">
+        <v>42.96875</v>
+      </c>
+      <c r="O20" s="17" t="n">
+        <v>49.609375</v>
+      </c>
+      <c r="P20" s="17" t="n">
+        <v>48.828125</v>
+      </c>
+      <c r="Q20" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>